--- a/排阵/混双大乱斗/混双大乱斗_对阵表.xlsx
+++ b/排阵/混双大乱斗/混双大乱斗_对阵表.xlsx
@@ -537,7 +537,7 @@
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>王小波/李祺祺</t>
+          <t>王小波/崔倩男</t>
         </is>
       </c>
     </row>
@@ -557,14 +557,14 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/高洁</t>
+          <t>陈顺星/李祺祺</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/滕菲</t>
+          <t>罗琴荩/高洁</t>
         </is>
       </c>
     </row>
@@ -584,14 +584,14 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/崔倩男</t>
+          <t>苏大哲/滕菲</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/李杏芝</t>
+          <t>黄冬青/崔倩男</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>王小波/田茜</t>
+          <t>王小波/李杏芝</t>
         </is>
       </c>
     </row>
@@ -638,14 +638,14 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/滕菲</t>
+          <t>陈顺星/田茜</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/高洁</t>
+          <t>罗琴荩/崔倩男</t>
         </is>
       </c>
     </row>
@@ -665,14 +665,14 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>林锋/崔倩男</t>
+          <t>林锋/高洁</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>王小波/李杏芝</t>
+          <t>王小波/李祺祺</t>
         </is>
       </c>
     </row>
@@ -692,14 +692,14 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/田茜</t>
+          <t>苏大哲/崔倩男</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/李祺祺</t>
+          <t>黄冬青/滕菲</t>
         </is>
       </c>
     </row>
@@ -719,14 +719,14 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>林锋/高洁</t>
+          <t>林锋/李杏芝</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>王小波/滕菲</t>
+          <t>王小波/田茜</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/李杏芝</t>
+          <t>罗琴荩/李祺祺</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/李祺祺</t>
+          <t>王小波/高洁</t>
         </is>
       </c>
     </row>
@@ -800,14 +800,14 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>王小波/高洁</t>
+          <t>林锋/崔倩男</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/田茜</t>
+          <t>苏大哲/田茜</t>
         </is>
       </c>
     </row>
@@ -827,14 +827,14 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>林锋/李杏芝</t>
+          <t>王小波/滕菲</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/李祺祺</t>
+          <t>黄冬青/李杏芝</t>
         </is>
       </c>
     </row>
@@ -854,14 +854,14 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/崔倩男</t>
+          <t>陈顺星/高洁</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/滕菲</t>
+          <t>罗琴荩/田茜</t>
         </is>
       </c>
     </row>
@@ -881,14 +881,14 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/田茜</t>
+          <t>苏大哲/李杏芝</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/高洁</t>
+          <t>黄冬青/李祺祺</t>
         </is>
       </c>
     </row>
@@ -908,14 +908,14 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>王小波/崔倩男</t>
+          <t>陈顺星/滕菲</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/李杏芝</t>
+          <t>罗琴荩/李杏芝</t>
         </is>
       </c>
     </row>
@@ -935,14 +935,14 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/李祺祺</t>
+          <t>苏大哲/李祺祺</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/高洁</t>
+          <t>黄冬青/田茜</t>
         </is>
       </c>
     </row>
@@ -962,14 +962,14 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/田茜</t>
+          <t>陈顺星/李杏芝</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/滕菲</t>
+          <t>苏大哲/高洁</t>
         </is>
       </c>
     </row>
@@ -989,14 +989,14 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/李杏芝</t>
+          <t>罗琴荩/滕菲</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/崔倩男</t>
+          <t>黄冬青/高洁</t>
         </is>
       </c>
     </row>
